--- a/data/puntos.xlsx
+++ b/data/puntos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hector.andagua\Downloads\Entel\ANALIZAR_ANTENAS_RUSEL\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{205CCEA5-30E4-4A29-912B-54B009C9B2D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{582147D8-2B63-4A95-8C71-A4AF52A13D9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{D66A7DA6-4E81-4053-8D9F-063A62F6676F}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>LATITUDE</t>
   </si>
@@ -42,18 +42,12 @@
     <t>LONGITUDE</t>
   </si>
   <si>
-    <t>KUSU HUBAIM</t>
-  </si>
-  <si>
     <t>-4.432080</t>
   </si>
   <si>
     <t>-78.249430</t>
   </si>
   <si>
-    <t>HUAMPANI</t>
-  </si>
-  <si>
     <t>-4.455675</t>
   </si>
   <si>
@@ -70,16 +64,64 @@
   </si>
   <si>
     <t>-78.15712768</t>
+  </si>
+  <si>
+    <t>KUSU KUBAIM</t>
+  </si>
+  <si>
+    <t>HUAMPAMI</t>
+  </si>
+  <si>
+    <t>IPARIA</t>
+  </si>
+  <si>
+    <t>-74.440360</t>
+  </si>
+  <si>
+    <t>-9.305730</t>
+  </si>
+  <si>
+    <t>NUEVA ITALIA</t>
+  </si>
+  <si>
+    <t>-9.8283617</t>
+  </si>
+  <si>
+    <t>-73.951520</t>
+  </si>
+  <si>
+    <t>BOLOGNESI</t>
+  </si>
+  <si>
+    <t>-10.029189</t>
+  </si>
+  <si>
+    <t>-73.955825</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.000000"/>
+  </numFmts>
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -102,15 +144,20 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{B16C0BCB-877A-4A68-BB34-126D229894CF}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -422,12 +469,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C73E505-D2DF-44AF-A399-5F4620DA12EB}">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -438,35 +485,68 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>3</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>11</v>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
